--- a/vehicle_inspection_forms/017_van_maintenance_checklist--vehicle_inspection_forms.xlsx
+++ b/vehicle_inspection_forms/017_van_maintenance_checklist--vehicle_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Vehicle Maintenance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Brake Pads and Fluid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Tire Maintenance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Battery and Electrical</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Vehicle Inspection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Brake Fluid Level</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Brake Fluid Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Vehicle Age</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Vehicle Type</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Maintenance Frequency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Last Service Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Van Maintenance Checklist Page 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Next Service Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,218 +870,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Van Maintenance Checklist</t>
+          <t>Vehicle Identification</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1148,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>battery_check</t>
+          <t>air_filter_check</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Battery Check</t>
+          <t>Air Filter Check</t>
         </is>
       </c>
     </row>
@@ -1182,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>brake_fluid_check</t>
+          <t>tire_condition_check</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brake Fluid Check</t>
+          <t>Tire Condition Check</t>
         </is>
       </c>
     </row>
@@ -1199,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>transmission_check</t>
+          <t>brake_fluid_check</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Transmission Check</t>
+          <t>Brake Fluid Check</t>
         </is>
       </c>
     </row>
@@ -1216,879 +1009,352 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tire_condition_check</t>
+          <t>spark_plug_check</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tire Condition Check</t>
+          <t>Spark Plug Check</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>air_filter_check</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air Filter Check</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fuel_filter_check</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fuel Filter Check</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>spark_plug_check</t>
+          <t>tire_rotation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spark Plug Check</t>
+          <t>Tire Rotation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>battery_terminals_check</t>
+          <t>tire_balance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Battery Terminals Check</t>
+          <t>Tire Balance</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>headlight_check</t>
+          <t>tire_alignment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Headlight Check</t>
+          <t>Tire Alignment</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>taillight_check</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taillight Check</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>brake_light_check</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brake Light Check</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>windshield_check</t>
+          <t>mineral_oil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Windshield Check</t>
+          <t>Mineral Oil</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>horn_check</t>
+          <t>synthetic_oil</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Horn Check</t>
+          <t>Synthetic Oil</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_10_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>steering_check</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steering Check</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>suspension_check</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Suspension Check</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>steering_fluid_check</t>
+          <t>suv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steering Fluid Check</t>
+          <t>SUV</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_1_choices</t>
+          <t>van_maintenance_checklist_page_11_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>axle_check</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Axle Check</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>oil_change</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oil Change</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_11_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tire_rotation</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tire Rotation</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_11_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>battery_replacement</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Battery Replacement</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_11_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>brake_pad_replacement</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brake Pad Replacement</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_16_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>spark_plug_replacement</t>
+          <t>make</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spark Plug Replacement</t>
+          <t>Make</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_16_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>air_filter_replacement</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Air Filter Replacement</t>
+          <t>Model</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
+          <t>van_maintenance_checklist_page_16_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fuel_filter_replacement</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fuel Filter Replacement</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>spark_plug_replacement</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Spark Plug Replacement</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>brake_fluid_replacement</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brake Fluid Replacement</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>brake_pads_replacement</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Brake Pads Replacement</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>tire_rotation</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tire Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>suspension_repair</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Suspension Repair</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>steering_adjustment</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Steering Adjustment</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_13_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_13_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Van Maintenance Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>van_maintenance_checklist_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
